--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486556_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486556_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3244</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2474</v>
+        <v>0.4965</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.923</v>
+        <v>0.0988</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.4305</v>
+        <v>1.3056</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.9371</v>
+        <v>-0.4259</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4933</v>
+        <v>1.7316</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3138</v>
+        <v>1.909</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1553</v>
+        <v>0.073</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8415</v>
+        <v>1.836</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.1167</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7819</v>
+        <v>-0.4989</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3348</v>
+        <v>-0.1044</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2976</v>
+        <v>0.4642</v>
       </c>
       <c r="T2" t="n">
-        <v>5.106</v>
+        <v>0.6321</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1915</v>
+        <v>-0.1679</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3698</v>
+        <v>-0.7395</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7602</v>
+        <v>-0.7395</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.1058</v>
       </c>
       <c r="E3" t="n">
-        <v>0.428</v>
+        <v>1.522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2529</v>
+        <v>-1.4162</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3056</v>
+        <v>-3.4305</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4259</v>
+        <v>-1.9371</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7316</v>
+        <v>-1.4933</v>
       </c>
       <c r="J3" t="n">
-        <v>1.909</v>
+        <v>-0.3138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.073</v>
+        <v>-1.1553</v>
       </c>
       <c r="L3" t="n">
-        <v>1.836</v>
+        <v>0.8415</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-3.1167</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4989</v>
+        <v>-0.7819</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1044</v>
+        <v>-2.3348</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5498</v>
+        <v>2.0789</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5636</v>
+        <v>2.3806</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0138</v>
+        <v>-0.3016</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7395</v>
+        <v>0.3698</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.335</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8278</v>
+        <v>-1.0513</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7471</v>
+        <v>0.7163</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8617</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>0.346</v>
+        <v>0.0916</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2776</v>
+        <v>0.0541</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1334</v>
+        <v>-1.102</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7619</v>
+        <v>0.0436</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3715</v>
+        <v>-1.1456</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.6648</v>
+        <v>-1.7515</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.961</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7037</v>
+        <v>-2.746</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6271</v>
+        <v>0.7692</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5776</v>
+        <v>1.6274</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0494</v>
+        <v>-0.8582</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0377</v>
+        <v>-2.5206</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3834</v>
+        <v>-0.6328</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6543</v>
+        <v>-1.8878</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.596</v>
+        <v>-0.1553</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4747</v>
+        <v>0.2319</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1214</v>
+        <v>-0.3873</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0067</v>
+        <v>-1.4417</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5837</v>
+        <v>-0.7619</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.423</v>
+        <v>-0.6797</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7515</v>
+        <v>-3.6648</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9945000000000001</v>
+        <v>-0.961</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.746</v>
+        <v>-2.7037</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7692</v>
+        <v>-1.6271</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6274</v>
+        <v>-0.5776</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8582</v>
+        <v>-1.0494</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5206</v>
+        <v>-2.0377</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6328</v>
+        <v>-0.3834</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8878</v>
+        <v>-1.6543</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.06</v>
+        <v>0.2878</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3953</v>
+        <v>0.4747</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6647</v>
+        <v>-0.1869</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1952</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.5947</v>
+        <v>-2.5966</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1593</v>
+        <v>-2.377</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4354</v>
+        <v>-0.2196</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7834</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5291</v>
+        <v>0.469</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0277</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5568</v>
+        <v>-0.341</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9347</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.727</v>
+        <v>-2.8338</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8203</v>
+        <v>-1.0812</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9067</v>
+        <v>-1.7526</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6445</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1472</v>
+        <v>0.746</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4506</v>
+        <v>1.1897</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5979</v>
+        <v>-0.4437</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7602</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.078900000000001</v>
+        <v>-6.4535</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.4881</v>
+        <v>-5.0785</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5908</v>
+        <v>-1.375</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0217</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9267</v>
+        <v>-0.3013</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2209</v>
+        <v>0.1887</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7058</v>
+        <v>-0.49</v>
       </c>
       <c r="V9" t="n">
         <v>0.1745</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.6713</v>
+        <v>-10.8832</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.8673</v>
+        <v>-7.2026</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.804</v>
+        <v>-3.6807</v>
       </c>
       <c r="G10" t="n">
         <v>-9.113300000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8994</v>
+        <v>0.6874</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5178</v>
+        <v>1.1825</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4951</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9347</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-25.2874</v>
+        <v>-24.9447</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.833</v>
+        <v>-15.4904</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.4544</v>
+        <v>-9.4543</v>
       </c>
       <c r="G11" t="n">
         <v>-25.9658</v>
@@ -1300,7 +1300,7 @@
         <v>-5.491400000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.960899999999999</v>
+        <v>-9.960900000000001</v>
       </c>
       <c r="P11" t="n">
         <v>-1.0875</v>
@@ -1312,13 +1312,13 @@
         <v>15.2256</v>
       </c>
       <c r="S11" t="n">
-        <v>4.0258</v>
+        <v>4.3683</v>
       </c>
       <c r="T11" t="n">
-        <v>6.8018</v>
+        <v>7.1443</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.7761</v>
+        <v>-2.776</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2598</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.213100000000001</v>
+        <v>8.561299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8959</v>
+        <v>5.0077</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3172</v>
+        <v>3.5536</v>
       </c>
       <c r="G12" t="n">
         <v>10.0729</v>
@@ -1390,13 +1390,13 @@
         <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2502</v>
+        <v>0.0979</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4386</v>
+        <v>0.5504</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6888</v>
+        <v>-0.4525</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7395</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0718</v>
+        <v>5.0309</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1102</v>
+        <v>1.032</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9616</v>
+        <v>3.9989</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0767</v>
+        <v>4.3235</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7341</v>
+        <v>2.9529</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3426</v>
+        <v>1.3706</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4473</v>
+        <v>2.3897</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0648</v>
+        <v>2.0622</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3825</v>
+        <v>0.3275</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6294</v>
+        <v>1.9338</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6693</v>
+        <v>0.8907</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0399</v>
+        <v>1.0431</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2349</v>
+        <v>-0.4449</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5128</v>
+        <v>0.2524</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2779</v>
+        <v>-0.6973</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5645</v>
+        <v>4.264</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4732</v>
+        <v>2.3197</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0913</v>
+        <v>1.9442</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3235</v>
+        <v>2.8985</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9529</v>
+        <v>-0.2921</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3706</v>
+        <v>3.1906</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3897</v>
+        <v>1.3001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0622</v>
+        <v>-1.3989</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3275</v>
+        <v>2.699</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9338</v>
+        <v>1.5984</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8907</v>
+        <v>1.1067</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0431</v>
+        <v>0.4916</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9113</v>
+        <v>0.2127</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3064</v>
+        <v>0.8244</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6048</v>
+        <v>-0.6117</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9347</v>
+        <v>-0.3698</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4502</v>
+        <v>3.809</v>
       </c>
       <c r="E15" t="n">
-        <v>2.655</v>
+        <v>1.031</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7952</v>
+        <v>2.778</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8985</v>
+        <v>3.6103</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2921</v>
+        <v>3.4733</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1906</v>
+        <v>0.1371</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3001</v>
+        <v>3.1371</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3989</v>
+        <v>2.4486</v>
       </c>
       <c r="L15" t="n">
-        <v>2.699</v>
+        <v>0.6885</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5984</v>
+        <v>0.4732</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1067</v>
+        <v>1.0247</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4916</v>
+        <v>-0.5514</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R15" t="n">
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.399</v>
+        <v>0.134</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1596</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7607</v>
+        <v>0.0427</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3698</v>
+        <v>0.9347</v>
       </c>
       <c r="W15" t="n">
         <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8822</v>
+        <v>3.3981</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3663</v>
+        <v>1.6573</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5159</v>
+        <v>1.7408</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6103</v>
+        <v>3.0767</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4733</v>
+        <v>2.7341</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1371</v>
+        <v>0.3426</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1371</v>
+        <v>1.4473</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4486</v>
+        <v>1.0648</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6885</v>
+        <v>0.3825</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4732</v>
+        <v>1.6294</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0247</v>
+        <v>1.6693</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5514</v>
+        <v>-0.0399</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2072</v>
+        <v>0.5612</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4266</v>
+        <v>1.0599</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2194</v>
+        <v>-0.4987</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9347</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9303</v>
+        <v>3.2816</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3603</v>
+        <v>2.8073</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.43</v>
+        <v>0.4743</v>
       </c>
       <c r="G17" t="n">
         <v>2.2872</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4216</v>
+        <v>-0.0703</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>0.1166</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0911</v>
+        <v>-0.1869</v>
       </c>
       <c r="V17" t="n">
         <v>1.4997</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6962</v>
+        <v>1.2794</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0138</v>
+        <v>0.2097</v>
       </c>
       <c r="F18" t="n">
-        <v>0.71</v>
+        <v>1.0697</v>
       </c>
       <c r="G18" t="n">
         <v>0.7938</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7725</v>
+        <v>-0.1893</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.442</v>
+        <v>-0.0823</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2166</v>
+        <v>0.2484</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4404</v>
+        <v>-0.2169</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2238</v>
+        <v>0.4653</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4424</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9694</v>
+        <v>-0.5044</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4899</v>
+        <v>-0.2485</v>
       </c>
       <c r="V19" t="n">
         <v>1.3252</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3825</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-3.5422</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3825</v>
+        <v>3.4548</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3825</v>
+        <v>1.014</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.7885</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3825</v>
+        <v>-1.7746</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-2.0434</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.4562</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.4997</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3825</v>
+        <v>3.0574</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3323</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3825</v>
+        <v>0.7251</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2037</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.4386</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.2349</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.926</v>
+        <v>-0.3825</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5161</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4099</v>
+        <v>-0.3825</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.3825</v>
       </c>
       <c r="H22" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8558</v>
+        <v>-0.3825</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4392</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4606</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5354</v>
+        <v>-0.3825</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8518</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3164</v>
+        <v>-0.3825</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2195</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1406</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3601</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6134</v>
+        <v>-0.7526</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4363</v>
+        <v>-0.8514</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8229</v>
+        <v>0.0988</v>
       </c>
       <c r="G23" t="n">
-        <v>1.014</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7885</v>
+        <v>0.952</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7746</v>
+        <v>-0.8558</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0434</v>
+        <v>-0.4392</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4562</v>
+        <v>-0.8998</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.4997</v>
+        <v>0.4606</v>
       </c>
       <c r="M23" t="n">
-        <v>3.0574</v>
+        <v>0.5354</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3323</v>
+        <v>1.8518</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7251</v>
+        <v>-1.3164</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2626</v>
+        <v>-0.2175</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3224</v>
+        <v>-1.0461</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4554</v>
+        <v>-0.1947</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8669</v>
+        <v>-0.8514</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-1.3252</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>25.2873</v>
+        <v>28.2677</v>
       </c>
       <c r="E24" t="n">
-        <v>9.4543</v>
+        <v>9.4542</v>
       </c>
       <c r="F24" t="n">
-        <v>15.833</v>
+        <v>18.8134</v>
       </c>
       <c r="G24" t="n">
         <v>25.9657</v>
@@ -2326,13 +2326,13 @@
         <v>16.313</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.025799999999999</v>
+        <v>-1.0455</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7759</v>
+        <v>2.776</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.801600000000001</v>
+        <v>-3.8215</v>
       </c>
       <c r="V24" t="n">
         <v>2.2598</v>
